--- a/samples/수주취합/고객사A_발주서.xlsx
+++ b/samples/수주취합/고객사A_발주서.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="79">
   <si>
     <t>사업장</t>
   </si>
@@ -222,6 +222,12 @@
     <t>KRW</t>
   </si>
   <si>
+    <t>15000</t>
+  </si>
+  <si>
+    <t>900000</t>
+  </si>
+  <si>
     <t>4500070002</t>
   </si>
   <si>
@@ -237,6 +243,12 @@
     <t>20261012</t>
   </si>
   <si>
+    <t>21000</t>
+  </si>
+  <si>
+    <t>840000</t>
+  </si>
+  <si>
     <t>4500070003</t>
   </si>
   <si>
@@ -250,6 +262,12 @@
   </si>
   <si>
     <t>20260920</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t>30000</t>
   </si>
 </sst>
 </file>
@@ -837,10 +855,10 @@
         <v>62</v>
       </c>
       <c r="S2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="T2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="U2" t="s">
         <v>55</v>
@@ -944,7 +962,7 @@
         <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
         <v>52</v>
@@ -959,16 +977,16 @@
         <v>55</v>
       </c>
       <c r="G3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
         <v>55</v>
       </c>
       <c r="I3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K3" t="s">
         <v>55</v>
@@ -983,7 +1001,7 @@
         <v>40</v>
       </c>
       <c r="O3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P3" t="s">
         <v>55</v>
@@ -995,10 +1013,10 @@
         <v>62</v>
       </c>
       <c r="S3" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="T3" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="U3" t="s">
         <v>55</v>
@@ -1102,7 +1120,7 @@
         <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
         <v>52</v>
@@ -1117,16 +1135,16 @@
         <v>55</v>
       </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H4" t="s">
         <v>55</v>
       </c>
       <c r="I4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K4" t="s">
         <v>55</v>
@@ -1141,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="P4" t="s">
         <v>55</v>
@@ -1153,10 +1171,10 @@
         <v>62</v>
       </c>
       <c r="S4" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="T4" t="s">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="U4" t="s">
         <v>55</v>
